--- a/시스템 기획/필드관련/테이블/필드 관련/Project βis_필드 데이터 테이블 속성 및 도메인 기획.xlsx
+++ b/시스템 기획/필드관련/테이블/필드 관련/Project βis_필드 데이터 테이블 속성 및 도메인 기획.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addmin\Desktop\Unity\Project βis\시스템 기획\필드관련\테이블\필드 관련\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33324E7-B8E8-4466-861D-629D3C355864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06175D45-93ED-450C-8032-CC9EB62DFA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4905" yWindow="2715" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="속성 정의" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
   <si>
     <t>FieldId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -167,6 +167,14 @@
   </si>
   <si>
     <t>필드에 배치될 랜덤 배치 이벤트성 상호작용의 수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExtraFieldMaxCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필드당 생성될 수 있는 최대 추가 생성 횟수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -573,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G9"/>
+  <dimension ref="B2:G10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
@@ -740,6 +748,26 @@
         <v>0</v>
       </c>
       <c r="G9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="b">
         <v>0</v>
       </c>
     </row>

--- a/시스템 기획/필드관련/테이블/필드 관련/Project βis_필드 데이터 테이블 속성 및 도메인 기획.xlsx
+++ b/시스템 기획/필드관련/테이블/필드 관련/Project βis_필드 데이터 테이블 속성 및 도메인 기획.xlsx
@@ -8,14 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addmin\Desktop\Unity\Project βis\시스템 기획\필드관련\테이블\필드 관련\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06175D45-93ED-450C-8032-CC9EB62DFA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5D0467-8174-4932-9AB8-3ECB98875036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="속성 정의" sheetId="1" r:id="rId1"/>
-    <sheet name="FieldTendency 도메인 정의" sheetId="2" r:id="rId2"/>
-    <sheet name="FieldSize 도메인 정의" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,24 +25,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
   <si>
     <t>FieldId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FieldTendency</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>속성 명칭</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FieldSize</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NextField</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -54,9 +44,6 @@
   </si>
   <si>
     <t>설명</t>
-  </si>
-  <si>
-    <t>설명</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -71,69 +58,10 @@
     <t>Integer</t>
   </si>
   <si>
-    <t>Enum</t>
-  </si>
-  <si>
     <t>필드를 구분하는 아이디</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>경향성 명칭</t>
-  </si>
-  <si>
-    <t>방사형</t>
-  </si>
-  <si>
-    <t>중앙을 중심으로 6갈레로 뻣어나가는 형태의 경향성</t>
-  </si>
-  <si>
-    <t>1자형</t>
-  </si>
-  <si>
-    <t>직선으로 이루어진 형태의 경향성</t>
-  </si>
-  <si>
-    <t>곡선형</t>
-  </si>
-  <si>
-    <t>곡선으로 이루어진 형태의 경향성</t>
-  </si>
-  <si>
-    <t>바둑형</t>
-  </si>
-  <si>
-    <t xml:space="preserve">바둑판, 우물 정井자 문양이 교차하는 형태의 경향성 </t>
-  </si>
-  <si>
-    <t>크기 단위</t>
-  </si>
-  <si>
-    <t>소형</t>
-  </si>
-  <si>
-    <t>15 * 15 타일 사이즈 필드</t>
-  </si>
-  <si>
-    <t>중형</t>
-  </si>
-  <si>
-    <t>30 * 30 타일 사이즈 필드</t>
-  </si>
-  <si>
-    <t>대형</t>
-  </si>
-  <si>
-    <t>45 * 45 타일 사이즈 필드</t>
-  </si>
-  <si>
-    <t>필드 생성 경향성을 Enum화한 속성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>필드의 사이즈를 Enum화한 속성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Null허용 여부</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -166,15 +94,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>필드에 배치될 랜덤 배치 이벤트성 상호작용의 수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExtraFieldMaxCount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>필드당 생성될 수 있는 최대 추가 생성 횟수</t>
+    <t>NTCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필드에 배치될 템플릿의 수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinTreeDeep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>종료 템플릿이 배치될 수 있는 최소 트리 깊이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필드에 배치될 랜덤 배치 탐색 이벤트의 수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -182,7 +118,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,23 +133,6 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -223,7 +142,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -231,76 +150,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -581,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G10"/>
+  <dimension ref="B2:G9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
@@ -593,22 +448,22 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
       <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
         <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
@@ -619,13 +474,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -633,16 +488,16 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C4" t="b">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
@@ -653,16 +508,16 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C5" t="b">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
@@ -673,19 +528,19 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" t="b">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -693,16 +548,16 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C7" t="b">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -713,16 +568,16 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -733,158 +588,34 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C9" t="b">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
       <c r="G9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C1048576 G3:G1048576" xr:uid="{5CFA7898-CE2B-4DE7-AA7E-6DEF1877FBCF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C11:C1048576 G3:G9 G11:G1048576 C3:C9" xr:uid="{5CFA7898-CE2B-4DE7-AA7E-6DEF1877FBCF}">
       <formula1>"True, False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E1048576" xr:uid="{280D11FB-513F-4473-8BC0-A0EF636DCD7D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E11:E1048576 E3:E9" xr:uid="{280D11FB-513F-4473-8BC0-A0EF636DCD7D}">
       <formula1>"Integer, Float, String, Enum, Boolean"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B9BCAF1-A77D-488D-A88A-64AAFCE45297}">
-  <dimension ref="B1:C6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="50.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCD4B34-A73D-4B35-AC98-8E1CC43B81D4}">
-  <dimension ref="B1:C5"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="10.25" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>